--- a/data_extactor/batch_10_fa/batch_0065_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0065_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ADP Workforce Now | Adobe Acrobat | Apple macOS | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | نرم‌افزار دفترداری | نرم‌افزار رایانش ابری Citrix | نرم‌افزار مدیریت قرارداد | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | Delphi Technology | نرم‌افزار سیستم مدیریت اسناد | Dropbox | Evernote | Facebook | FileMaker Pro | نرم‌افزار حسابداری وجوه امانی | Google Docs | Google Drive | GroupMe | HCSS HeavyBid | HCSS HeavyJob | نرم‌افزار دستگاه کامپیوتر جیبی | سیستم کدگذاری رویه مشترک مراقبت‌های بهداشتی HCPCS | Henry Schein Dentrix | نرم‌افزار مدیریت منابع انسانی HRMS | IBM Cognos Impromptu | IBM Domino | IBM Notes | IBM SPSS Statistics | Intuit QuickBooks | JamBoard | LexisNexis | LogMeIn GoToMeeting | Loom | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه پزشکی | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Windows | Microsoft Word | Minitab | Mozilla Firefox | Nearpod | NetSuite ERP | نرم‌افزار امنیت سایبری NortonLifeLock | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Taleo | Padlet | نرم‌افزار حقوق و دستمزد | Qlik Tech QlikView | Quicken | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | Sage 50 Accounting | نرم‌افزار Salesforce | Screencastify | Slack | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | Tableau | نرم‌افزار مالیات | نرم‌افزار مرورگر وب | نرم‌افزار برنامه‌ریزی کاری | نرم‌افزار Yardi | YouTube</t>
+          <t>ADP Workforce Now | Adobe Acrobat | Apple macOS | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | نرم‌افزار حسابداری | نرم‌افزار رایانش ابری Citrix | نرم‌افزار مدیریت قرارداد | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | Delphi Technology | نرم‌افزار سیستم مدیریت اسناد | Dropbox | Evernote | Facebook | FileMaker Pro | نرم‌افزار حسابداری صندوق | Google Docs | Google Drive | GroupMe | HCSS HeavyBid | HCSS HeavyJob | نرم‌افزار دستگاه‌های کامپیوتر جیبی | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Henry Schein Dentrix | نرم‌افزار مدیریت منابع انسانی HRMS | IBM Cognos Impromptu | IBM Domino | IBM Notes | IBM SPSS Statistics | Intuit QuickBooks | JamBoard | LexisNexis | LogMeIn GoToMeeting | Loom | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Windows | Microsoft Word | Minitab | Mozilla Firefox | Nearpod | NetSuite ERP | نرم‌افزار امنیت سایبری NortonLifeLock | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Taleo | Padlet | نرم‌افزار حقوق و دستمزد | Qlik Tech QlikView | Quicken | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | Sage 50 Accounting | نرم‌افزار Salesforce | Screencastify | Slack | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | Tableau | نرم‌افزار مالیاتی | نرم‌افزار مرورگر وب | نرم‌افزار زمان‌بندی کار | نرم‌افزار Yardi | YouTube</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>مانیتورینگ | سخن‌گفتن | گوش‌دادن فعالانه | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعالانه | استراتژی‌های یادگیری</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | خدمات مشتریان و شخصی | زبان انگلیسی | اداری | کامپیوتر و الکترونیک | پرسنل و منابع انسانی | اقتصاد و حسابداری</t>
+          <t>مدیریت و اداره | خدمات مشتری و شخصی | زبان انگلیسی | اداری | رایانه و الکترونیک | پرسنل و منابع انسانی | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی به اطلاعات | دید نزدیک | استدلال استقرایی | اصالت | روان بودن ایده‌ها | انعطاف‌پذیری دسته‌بندی | توجه انتخابی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | بینایی نزدیک | استدلال استقرایی | اصالت | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان به صورت نشسته | اهمیت دقیق یا منظم بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | آزادی در تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | داخل ساختمان، محیط کنترل‌شده | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | سرپرستان خط اول مشاغل ساختمانی و استخراج | سرپرستان خط اول کارکنان تفریحی و سرگرمی، به جز خدمات قمار | سرپرستان خط اول کارکنان تهیه و سرو غذا | سرپرستان خط اول دستیاران، کارگران و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارکنان خانه‌داری و سرایداری | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصب‌کنندگان و تعمیرکاران | سرپرستان خط اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول مهمانداران مسافران | سرپرستان خط اول کارکنان خدمات شخصی | سرپرستان خط اول کارکنان تولید و عملیات | سرپرستان خط اول کارکنان فروش خرده‌فروشی | سرپرستان خط اول کارکنان امنیتی | مدیران عمومی و عملیاتی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | متخصصان منابع انسانی | تحلیلگران مدیریت | کارمندان دفتری، عمومی | متخصصان مدیریت پروژه</t>
+          <t>مدیران خدمات اداری | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کارگران خدمات شخصی | سرپرستان رده اول کارگران تولید و بهره‌برداری | سرپرستان رده اول کارکنان فروش خرده‌فروشی | سرپرستان خط اول کارکنان امنیتی | مدیران عمومی و عملیات | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | متخصصان منابع انسانی | تحلیل‌گران مدیریت | کارمندان دفتری عمومی | متخصصان مدیریت پروژه</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعالانه | سخن‌گفتن | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | اداری | کامپیوتر و الکترونیک | مخابرات</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | رایانه و الکترونیک | مخابرات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | دید نزدیک | توجه انتخابی | ترتیب‌دهی به اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان کتبی | درک کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان کتبی | درک کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | ارتباط با دیگران | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | کار با یا مشارکت در یک گروه کاری یا تیم | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | داخل ساختمان، محیط کنترل‌شده | اهمیت دقیق یا منظم بودن | نامه‌ها و یادداشت‌های کتبی | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | صرف زمان به صورت نشسته | صرف زمان برای انجام حرکات تکراری | موقعیت‌های تعارض | اهمیت تکرار وظایف مشابه | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>مکالمات تلفنی | ارتباط با دیگران | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | صرف زمان برای انجام حرکات تکراری | موقعیت‌های تعارض | اهمیت تکرار وظایف یکسان | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | کارمندان صدور صورتحساب و ثبت | کارمندان کارگزاری | نمایندگان خدمات مشتریان | کاربران ورود داده | متصدیان ارسال، به جز پلیس، آتش‌نشانی و آمبولانس | منشی‌های اجرایی و دستیاران اداری اجرایی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | کارمندان پست و اپراتورهای ماشین‌های پستی، به جز خدمات پستی | منشی‌های پزشکی و دستیاران اداری | کارمندان دفتری، عمومی | کارمندان خدمات پستی | اپراتورهای مخابراتی امنیت عمومی | پذیرشگران و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | متخصصان مهندسی مخابرات | نصب‌کنندگان و تعمیرکاران تجهیزات مخابراتی، به جز نصب‌کنندگان خطوط | بازاریابان تلفنی | اپراتورهای تلفن | پردازشگران کلمات و تایپیست‌ها</t>
+          <t>مدیران خدمات اداری | کارمندان صدور صورتحساب و ثبت | کارمندان کارگزاری | نمایندگان خدمات مشتریان | اپراتورهای ورود داده | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | منشی‌های اجرایی و دستیاران اداری اجرایی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | کارمندان پست و اپراتورهای ماشین‌های پست، به جز اداره پست | منشی‌های پزشکی و دستیاران اداری | کارمندان دفتری عمومی | کارمندان خدمات پستی | اپراتورهای مخابراتی امنیت عمومی | متصدیان پذیرش و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | بازاریابان تلفنی | اپراتورهای تلفن | واژه‌پردازان و تایپیست‌ها</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>نرم‌افزار اعزام به کمک کامپیوتر | نرم‌افزار دستگاه کامپیوتر جیبی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | نرم‌افزار ویدئو کنفرانس</t>
+          <t>نرم‌افزار اعزام به کمک کامپیوتر | نرم‌افزار دستگاه‌های کامپیوتر جیبی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | نرم‌افزار ویدئو کنفرانس</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن‌گفتن | گوش‌دادن فعالانه | تفکر انتقادی | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | مخابرات | اداری | زبان انگلیسی | کامپیوتر و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | مخابرات | اداری | زبان انگلیسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | دید نزدیک | توجه انتخابی | حساسیت به مسئله | درک کتبی</t>
+          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | توجه انتخابی | حساسیت به مسئله | درک کتبی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | مکالمات تلفنی | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | داخل ساختمان, محیط کنترل‌شده | فراوانی تصمیم‌گیری | اهمیت دقیق یا منظم بودن | صرف زمان برای انجام حرکات تکراری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت تکرار وظایف مشابه | صرف زمان به صورت نشسته | تاثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | قرار گرفتن در معرض صداها و سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند</t>
+          <t>ارتباط با دیگران | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن | صرف زمان برای انجام حرکات تکراری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت تکرار وظایف یکسان | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارمندان صدور صورتحساب و ثبت | صندوقداران | متخصصان پشتیبانی شبکه کامپیوتری | نمایندگان خدمات مشتریان | کاربران ورود داده | متصدیان ارسال، به جز پلیس، آتش‌نشانی و آمبولانس | کارمندان بایگانی | کارمندان خسارت بیمه و پردازش بیمه‌نامه | مصاحبه‌کنندگان، به جز واجدین شرایط و وام | منشی‌های پزشکی و دستیاران اداری | کارمندان دفتری، عمومی | اپراتورهای مخابراتی امنیت عمومی | پذیرشگران و کارمندان اطلاعات | نمایندگان بلیط رزرو و حمل‌ونقل و کارمندان سفر | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | اپراتورهای تلفنخانه، شامل سرویس پاسخگویی | نصب‌کنندگان و تعمیرکاران تجهیزات مخابراتی، به جز نصب‌کنندگان خطوط | بازاریابان تلفنی | پردازشگران کلمات و تایپیست‌ها</t>
+          <t>کارمندان صدور صورتحساب و ثبت | صندوق‌داران | متخصصان پشتیبانی شبکه کامپیوتری | نمایندگان خدمات مشتریان | اپراتورهای ورود داده | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | کارمندان بایگانی | کارمندان پردازش بیمه و بیمه‌نامه | مصاحبه‌کنندگان، به جز واجدین شرایط و وام | منشی‌های پزشکی و دستیاران اداری | کارمندان دفتری عمومی | اپراتورهای مخابراتی امنیت عمومی | متصدیان پذیرش و کارمندان اطلاعات | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | اپراتورهای تلفنخانه، شامل سرویس پاسخگویی | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | بازاریابان تلفنی | واژه‌پردازان و تایپیست‌ها</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | نرم‌افزار Microsoft Office | نرم‌افزار ایمیل | Microsoft Access | Microsoft SharePoint | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | Google Docs | نرم‌افزار مدیریت تقویم | برنامه‌های صفحه‌گسترده | Adobe Acrobat | نرم‌افزار برنامه‌ریزی</t>
+          <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | نرم‌افزار Microsoft Office | نرم‌افزار ایمیل | Microsoft Access | Microsoft SharePoint | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | Google Docs | نرم‌افزار مدیریت تقویم | برنامه‌های صفحه‌گسترده | Adobe Acrobat | نرم‌افزار زمان‌بندی</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعالانه | سخن‌گفتن | درک مطلب | تفکر انتقادی | مانیتورینگ | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مخابرات | خدمات مشتریان و شخصی | زبان انگلیسی | کامپیوتر و الکترونیک | ارتباطات و رسانه | امنیت و ایمنی عمومی</t>
+          <t>مخابرات | خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | ارتباطات و رسانه | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اشتراک زمانی | چالاکی انگشتان | چالاکی دست | دید دور | حفظ‌کردن | روان بودن ایده‌ها | توجه شنیداری | سرعت ادراکی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | توجه شنیداری | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | داخل ساختمان، محیط کنترل‌شده | صرف زمان به صورت نشسته | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا منظم بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | اهمیت تکرار وظایف مشابه | میزان خودکارسازی | صرف زمان برای انجام حرکات تکراری</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | میزان خودکارسازی | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورهای تلفنخانه، شامل سرویس پاسخگویی | اپراتورهای تلفن | اپراتورهای مخابراتی امنیت عمومی | متصدیان ارسال، به جز پلیس، آتش‌نشانی و آمبولانس | نمایندگان خدمات مشتریان | پذیرشگران و کارمندان اطلاعات | نمایندگان بلیط رزرو و حمل‌ونقل و کارمندان سفر | کارمندان ثبت سفارش | کارمندان مکاتبات | کاربران ورود داده | کارمندان دفتری، عمومی | کارمندان اطلاعات و ثبت سوابق، همه موارد دیگر | نمایندگان باربری و حمل‌ونقل کالا | پیک‌ها و نامه‌رسان‌ها | بازاریابان تلفنی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | متخصصان پشتیبانی کاربران کامپیوتر | نصب‌کنندگان و تعمیرکاران تجهیزات مخابراتی، به جز نصب‌کنندگان خطوط | پردازشگران کلمات و تایپیست‌ها | کارکنان پشتیبانی دفتری و اداری، همه موارد دیگر</t>
+          <t>اپراتورهای تلفنخانه، شامل سرویس پاسخگویی | اپراتورهای تلفن | اپراتورهای مخابراتی امنیت عمومی | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | نمایندگان خدمات مشتریان | متصدیان پذیرش و کارمندان اطلاعات | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | کارمندان ثبت سفارش | کارمندان مکاتبات | اپراتورهای ورود داده | کارمندان دفتری عمومی | کارمندان اطلاعات و ثبت سوابق، سایر | نمایندگان بار و محموله | پیک‌ها و نامه‌رسان‌ها | بازاریابان تلفنی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | متخصصان پشتیبانی کاربران کامپیوتر | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | واژه‌پردازان و تایپیست‌ها | کارکنان پشتیبانی دفتری و اداری، همه موارد دیگر</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ADP Drive DMS for Accounting | ADS Advantage | Adtec Agency Manager | Austin Logistics CallSelect | نرم‌افزار پردازش CU Connect | Collection Data Systems CollectOne-Tiger | Columbia Ultimate Archive | Columbia Ultimate RPCS | Columbia Ultimate Remit | Data-Tel Ceasar | نرم‌افزار مدیریت و وصول حساب بدهی | نرم‌افزار کدگذاری تشخیصی و رویه‌ای | نرم‌افزار سیستم مدیریت اسناد | HMS | سیستم کدگذاری رویه مشترک مراقبت‌های بهداشتی HCPCS | Intuit QuickBooks | LexisNexis | LexisNexis Banko | MEDITECH software | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه پزشکی | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | NetSuite ERP | Ontario Systems FACS | نرم‌افزار تشخیص نوری کاراکتر OCR | Oracle JD Edwards EnterpriseOne | Quantrax Intelec | نرم‌افزار پایگاه داده رابطه‌ای | نرم‌افزار SAP | Sage 50 Accounting | System Innovators | TCI XML Credit Interface | W3 Data BatchAppend411 | نرم‌افزار مرورگر وب</t>
+          <t>ADP Drive DMS for Accounting | ADS Advantage | Adtec Agency Manager | Austin Logistics CallSelect | نرم‌افزار پردازش CU Connect | Collection Data Systems CollectOne-Tiger | Columbia Ultimate Archive | Columbia Ultimate RPCS | Columbia Ultimate Remit | Data-Tel Ceasar | نرم‌افزار مدیریت و وصول حساب بدهی | نرم‌افزار کدگذاری تشخیصی و فرآیندی | نرم‌افزار سیستم مدیریت اسناد | HMS | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Intuit QuickBooks | LexisNexis | LexisNexis Banko | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | NetSuite ERP | Ontario Systems FACS | نرم‌افزار تشخیص نوری کاراکتر OCR | Oracle JD Edwards EnterpriseOne | Quantrax Intelec | نرم‌افزار پایگاه داده رابطه‌ای | نرم‌افزار SAP | Sage 50 Accounting | System Innovators | TCI XML Credit Interface | W3 Data BatchAppend411 | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعالانه | سخن‌گفتن | نگارش | درک مطلب | تفکر انتقادی | مانیتورینگ</t>
+          <t>گوش دادن فعال | سخن گفتن | نگارش | درک مطلب | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و شخصی | ریاضیات | اقتصاد و حسابداری | قانون و مقررات دولتی | کامپیوتر و الکترونیک | اداری | مدیریت و امور اداری</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | اقتصاد و حسابداری | قانون و دولت | رایانه و الکترونیک | اداری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان کتبی | دید نزدیک | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان کتبی | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | داخل ساختمان، محیط کنترل‌شده | صرف زمان به صورت نشسته | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | مکالمات تلفنی | اهمیت تکرار وظایف مشابه | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا منظم بودن | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | ایمیل | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نامه‌ها و یادداشت‌های کتبی | موقعیت‌های تعارض | سطح رقابت | کار با یا مشارکت در یک گروه کاری یا تیم</t>
+          <t>ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | مکالمات تلفنی | اهمیت تکرار وظایف یکسان | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | ایمیل | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نامه‌ها و یادداشت‌های کتبی | موقعیت‌های تعارض | سطح رقابت | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | کارمندان مکاتبات | تحلیلگران اعتبار | تاییدکنندگان، بررسی‌کنندگان و کارمندان اعتبار | مشاوران اعتباری | نمایندگان خدمات مشتریان | مدیران مالی | کارمندان خسارت بیمه و پردازش بیمه‌نامه | مصاحبه‌کنندگان و کارمندان وام | افسران وام | کارمندان حساب‌های جدید | کارمندان ثبت سفارش | کارمندان حقوق و دستمزد و ثبت زمان | مشاوران مالی شخصی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | ممیزان و وصول‌کنندگان مالیات، و ماموران دارایی | تحویل‌داران بانک</t>
+          <t>حسابداران و حسابرسان | کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | کارمندان مکاتبات | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتبار | نمایندگان خدمات مشتریان | مدیران مالی | کارمندان پردازش بیمه و بیمه‌نامه | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | کارمندان حساب‌های جدید | کارمندان ثبت سفارش | کارمندان حقوق و دستمزد و ثبت زمان | مشاوران مالی شخصی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد | تحویل‌داران</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Accuity EPICWare | نرم‌افزار حقوقی Aderant | Allscripts Professional PM | نرم‌افزار صدور صورتحساب خودکار | CAI Software Seasoft | نرم‌افزار تصویربرداری چک | نرم‌افزار پردازش چک | نرم‌افزار کنترل مرتب‌سازی چک | نرم‌افزار پایگاه داده | Epic Systems | سیستم‌های مدیریت فایل | Fiserv PEP+ reACH | GE Healthcare Centricity EMR | سیستم کدگذاری رویه مشترک مراقبت‌های بهداشتی HCPCS | HelpIT Systems addressIT | IBM Cognos Impromptu | IPS of Boston DoubleCheck | Image Deposit Exchange Check Station | شبکه‌های تبادل تصویر | نرم‌افزار چاپ سند جایگزین تصویر IRD | Intuit QuickBooks | MEDITECH software | نرم‌افزار صدور صورتحساب پزشکی | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه پزشکی | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Windows | Microsoft Word | Mitek Systems ImageNet Payments | NetSuite ERP | نرم‌افزار تشخیص نوری کاراکتر OCR | Oracle E-Business Suite Financials | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft Financials | نرم‌افزار پرداخت مثبت | نرم‌افزار مدیریت مطب PMS | Prime Clinical | QuoteWerks | نرم‌افزار ثبت سپرده از راه دور | نرم‌افزار SAP | Sage 50 Accounting | Sage Medical Manager | Thomson Reuters Elite Enterprise | VECTORsgi Check Management Solution | VECTORsgi Image Exchange Solution | نرم‌افزار مرورگر وب | eMDs Medisoft</t>
+          <t>Accuity EPICWare | نرم‌افزار حقوقی Aderant | Allscripts Professional PM | نرم‌افزار صدور صورتحساب خودکار | CAI Software Seasoft | نرم‌افزار تصویربرداری چک | نرم‌افزار پردازش چک | نرم‌افزار کنترل مرتب‌سازی چک | نرم‌افزار پایگاه داده | Epic Systems | سیستم‌های مدیریت فایل | Fiserv PEP+ reACH | GE Healthcare Centricity EMR | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | HelpIT Systems addressIT | IBM Cognos Impromptu | IPS of Boston DoubleCheck | Image Deposit Exchange Check Station | شبکه‌های تبادل تصویر | نرم‌افزار چاپ سند جایگزین تصویر IRD | Intuit QuickBooks | نرم‌افزار MEDITECH | نرم‌افزار صدور صورتحساب پزشکی | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Windows | Microsoft Word | Mitek Systems ImageNet Payments | NetSuite ERP | نرم‌افزار تشخیص نوری کاراکتر OCR | Oracle E-Business Suite Financials | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft Financials | نرم‌افزار پرداخت مثبت | نرم‌افزار مدیریت مطب PMS | Prime Clinical | QuoteWerks | نرم‌افزار ثبت سپرده از راه دور | نرم‌افزار SAP | Sage 50 Accounting | Sage Medical Manager | Thomson Reuters Elite Enterprise | VECTORsgi Check Management Solution | VECTORsgi Image Exchange Solution | نرم‌افزار مرورگر وب | eMDs Medisoft</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | ریاضیات | گوش‌دادن فعالانه | سخن‌گفتن | تفکر انتقادی | مانیتورینگ | نگارش</t>
+          <t>درک مطلب | ریاضیات | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>اداری | خدمات مشتریان و شخصی | زبان انگلیسی | اقتصاد و حسابداری | ریاضیات | کامپیوتر و الکترونیک | مدیریت و امور اداری</t>
+          <t>اداری | خدمات مشتری و شخصی | زبان انگلیسی | اقتصاد و حسابداری | ریاضیات | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک کتبی | ترتیب‌دهی به اطلاعات | بیان شفاهی | تشخیص گفتار | بیان کتبی | درک شفاهی | حساسیت به مسئله | وضوح گفتار | توانایی کار با اعداد | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | استدلال استقرایی</t>
+          <t>بینایی نزدیک | درک کتبی | ترتیب‌دهی اطلاعات | بیان شفاهی | تشخیص گفتار | بیان کتبی | درک شفاهی | حساسیت به مسئله | وضوح گفتار | توانایی عددی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | صرف زمان به صورت نشسته | اهمیت تکرار وظایف مشابه | ارتباط با دیگران | اهمیت دقیق یا منظم بودن | تعیین وظایف، اولویت‌ها و اهداف | داخل ساختمان، محیط کنترل‌شده | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری</t>
+          <t>ایمیل | مکالمات تلفنی | صرف زمان برای نشستن | اهمیت تکرار وظایف یکسان | ارتباط با دیگران | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | وصول‌کنندگان قبوض و حساب‌ها | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | کارمندان مکاتبات | تاییدکنندگان، بررسی‌کنندگان و کارمندان اعتبار | نمایندگان خدمات مشتریان | کارمندان بایگانی | مدیران مالی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | کارمندان خسارت بیمه و پردازش بیمه‌نامه | کارمندان دفتری، عمومی | کارمندان ثبت سفارش | کارمندان حقوق و دستمزد و ثبت زمان | کارمندان خدمات پستی | کارمندان تدارکات | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | کارمندان ارسال، دریافت و موجودی | ممیزان و وصول‌کنندگان مالیات، و ماموران دارایی | تحویل‌داران بانک</t>
+          <t>حسابداران و حسابرسان | وصول‌کنندگان قبوض و حساب‌ها | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | کارمندان مکاتبات | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | نمایندگان خدمات مشتریان | کارمندان بایگانی | مدیران مالی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | کارمندان پردازش بیمه و بیمه‌نامه | کارمندان دفتری عمومی | کارمندان ثبت سفارش | کارمندان حقوق و دستمزد و ثبت زمان | کارمندان خدمات پستی | کارمندان تدارکات | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | کارمندان ارسال، دریافت و موجودی کالا | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد | تحویل‌داران</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ACS Technologies ACS Financial Suite | ADP Pay eXpert | ADP Workforce Now | AMS Services AMS Sagitta | ATX Total Accounting Office | ATX Total Engagement Office | نرم‌افزار حساب‌های پرداختنی | نرم‌افزار حساب‌های دریافتنی | Accurate NXG | AcornSystems Corporate Performance Management | Act! | Activant Solutions Activant Prophet 21 | AdaptaSoft CyberPay | Adobe Acrobat | Advanced Management Systems Software for Wineries | American HealthTech Financial | نرم‌افزار مدیریت دارایی | نرم‌افزار گزارش‌دهی مالی و حسابرسی AuditWare | نرم‌افزار حسابرسی | Automation Counselors municiPAL | BLS Software Invoice! | Best MIP Fund Accounting | Blackbaud The Financial Edge | Blackbaud The Raiser's Edge | نرم‌افزار مدیریت عملکرد کسب‌وکار BPM | CCIS AccountAbility | CYMA IV Accounting for Windows | Cartesis ES Magnitude | نرم‌افزار حسابداری ساخت‌وساز ComputerEase | Corporate Responsibility System Technologies Limited CRSTL Compliance Positioning System | نرم‌افزار حسابداری بهای تمام‌شده | سیستم کنترل اطلاعات مشتری CICS | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | Delphi Technology | نرم‌افزار سیستم مدیریت اسناد | Dropbox | Epic Systems | FaceTime | Fifth Walk BillingTracker | FileMaker Pro | نرم‌افزار انطباق مالی | نرم‌افزار گزارش‌دهی مالی | نرم‌افزار صورت‌های مالی | FlexiFinancials FlexiLedger | نرم‌افزار حسابداری وجوه امانی | نرم‌افزار دفتر کل | Google Docs | Google Drive | HCSS HeavyBid | HCSS HeavyJob | HMS | سیستم کدگذاری رویه مشترک مراقبت‌های بهداشتی HCPCS | Heron CrossTie General Ledger | نرم‌افزار مدیریت منابع انسانی HRMS | IBM Cognos Impromptu | IBM Notes | Infor Global Solutions Starbuilder | Intrax ProcedureNet | Intuit QuickBooks | نرم‌افزار مدیریت سوابق Iron Mountain Accutrac | LexisNexis | MEDITECH software | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه پزشکی | MethodWare ProAudit Advisor | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Windows | Microsoft Word | NetSuite ERP | New Millennium Communications Genesis Accounting | OmniRIM Records Management Suite | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | PROPHIX Enterprise | Paisley AutoAudit | Paisley Cardmap | Paisley Focus Control Assurance | Paisley IssueTrack | Paisley RiskNavigator | نرم‌افزار حقوق و دستمزد | سیستم کار حسابرسی Pentana PAWS | Quicken | RSM McGladrey Advanced Practice Solutions Paperless Audit | RSM McGladrey Auditor Assistant | نرم‌افزار مدیریت سوابق | Roundtable Software Advantage Accounting System | SAP Business Objects | SAP BusinessObjects Data Integrator | SAP Concur | SAP Crystal Reports | نرم‌افزار SAP | Sage 100 Contractor | Sage 100 ERP | Sage 50 Accounting | Sage EDP Payroll Tax | Skype | Softrax Revenue Management | نرم‌افزار مالیات | Tumbleweed SecureTransport | UA Business Software Professional Edition | نرم‌افزار Yardi</t>
+          <t>ACS Technologies ACS Financial Suite | ADP Pay eXpert | ADP Workforce Now | AMS Services AMS Sagitta | ATX Total Accounting Office | ATX Total Engagement Office | نرم‌افزار حساب‌های پرداختنی | نرم‌افزار حساب‌های دریافتنی | Accurate NXG | AcornSystems Corporate Performance Management | Act! | Activant Solutions Activant Prophet 21 | AdaptaSoft CyberPay | Adobe Acrobat | Advanced Management Systems Software for Wineries | American HealthTech Financial | نرم‌افزار مدیریت دارایی | نرم‌افزار گزارش‌دهی مالی و حسابرسی AuditWare | نرم‌افزار حسابرسی | Automation Counselors municiPAL | BLS Software Invoice! | Best MIP Fund Accounting | Blackbaud The Financial Edge | Blackbaud The Raiser's Edge | نرم‌افزار مدیریت عملکرد کسب‌وکار BPM | CCIS AccountAbility | CYMA IV Accounting for Windows | Cartesis ES Magnitude | نرم‌افزار حسابداری ساخت‌وساز ComputerEase | Corporate Responsibility System Technologies Limited CRSTL Compliance Positioning System | نرم‌افزار حسابداری هزینه | سیستم کنترل اطلاعات مشتری CICS | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | Delphi Technology | نرم‌افزار سیستم مدیریت اسناد | Dropbox | Epic Systems | FaceTime | Fifth Walk BillingTracker | FileMaker Pro | نرم‌افزار انطباق مالی | نرم‌افزار گزارش‌دهی مالی | نرم‌افزار صورت‌های مالی | FlexiFinancials FlexiLedger | نرم‌افزار حسابداری صندوق | نرم‌افزار دفتر کل | Google Docs | Google Drive | HCSS HeavyBid | HCSS HeavyJob | HMS | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Heron CrossTie General Ledger | نرم‌افزار مدیریت منابع انسانی HRMS | IBM Cognos Impromptu | IBM Notes | Infor Global Solutions Starbuilder | Intrax ProcedureNet | Intuit QuickBooks | Iron Mountain Accutrac records management software | LexisNexis | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | MethodWare ProAudit Advisor | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Windows | Microsoft Word | NetSuite ERP | New Millennium Communications Genesis Accounting | OmniRIM Records Management Suite | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | PROPHIX Enterprise | Paisley AutoAudit | Paisley Cardmap | Paisley Focus Control Assurance | Paisley IssueTrack | Paisley RiskNavigator | نرم‌افزار حقوق و دستمزد | Pentana audit work system PAWS | Quicken | RSM McGladrey Advanced Practice Solutions Paperless Audit | RSM McGladrey Auditor Assistant | نرم‌افزار مدیریت سوابق | Roundtable Software Advantage Accounting System | SAP Business Objects | SAP BusinessObjects Data Integrator | SAP Concur | SAP Crystal Reports | نرم‌افزار SAP | Sage 100 Contractor | Sage 100 ERP | Sage 50 Accounting | Sage EDP Payroll Tax | Skype | Softrax Revenue Management | نرم‌افزار مالیاتی | Tumbleweed SecureTransport | UA Business Software Professional Edition | نرم‌افزار Yardi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ریاضیات | تفکر انتقادی | گوش‌دادن فعالانه | درک مطلب | نگارش | سخن‌گفتن | مانیتورینگ</t>
+          <t>ریاضیات | تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | اداری | ریاضیات | زبان انگلیسی | اقتصاد و حسابداری | کامپیوتر و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | اداری | ریاضیات | زبان انگلیسی | اقتصاد و حسابداری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | استدلال ریاضی | دید نزدیک | درک کتبی | بیان کتبی | توانایی کار با اعداد | حساسیت به مسئله | بیان شفاهی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی به اطلاعات | استدلال استقرایی | وضوح گفتار | توجه انتخابی | استدلال قیاسی</t>
+          <t>درک شفاهی | استدلال ریاضی | بینایی نزدیک | درک کتبی | بیان کتبی | توانایی عددی | حساسیت به مسئله | بیان شفاهی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | وضوح گفتار | توجه انتخابی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | داخل ساختمان، محیط کنترل‌شده | مکالمات تلفنی | اهمیت دقیق یا منظم بودن | اهمیت تکرار وظایف مشابه | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان به صورت نشسته | صرف زمان برای انجام حرکات تکراری | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با مشتریان خارجی یا عموم مردم به طور کلی</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان برای نشستن | صرف زمان برای انجام حرکات تکراری | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | وصول‌کنندگان قبوض و حساب‌ها | کارمندان صدور صورتحساب و ثبت | کارمندان کارگزاری | کارمندان مکاتبات | تحلیلگران اعتبار | تاییدکنندگان، بررسی‌کنندگان و کارمندان اعتبار | کارمندان بایگانی | مدیران مالی | کارمندان خسارت بیمه و پردازش بیمه‌نامه | مصاحبه‌کنندگان و کارمندان وام | افسران وام | کارمندان حساب‌های جدید | کارمندان دفتری، عمومی | کارمندان حقوق و دستمزد و ثبت زمان | نمایندگان فروش اوراق بهادار، کالا و خدمات مالی | دستیاران آماری | ممیزان و وصول‌کنندگان مالیات، و ماموران دارایی | تهیه‌کنندگان اظهارنامه مالیاتی | تحویل‌داران بانک</t>
+          <t>حسابداران و حسابرسان | وصول‌کنندگان قبوض و حساب‌ها | کارمندان صدور صورتحساب و ثبت | کارمندان کارگزاری | کارمندان مکاتبات | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | کارمندان بایگانی | مدیران مالی | کارمندان پردازش بیمه و بیمه‌نامه | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | کارمندان حساب‌های جدید | کارمندان دفتری عمومی | کارمندان حقوق و دستمزد و ثبت زمان | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | دستیاران آماری | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد | تهیه‌کنندگان اظهارنامه مالیاتی | تحویل‌داران</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن‌گفتن | گوش‌دادن فعالانه | ریاضیات | مانیتورینگ | تفکر انتقادی | نگارش | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | ریاضیات | نظارت | تفکر انتقادی | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | ریاضیات | زبان انگلیسی | مدیریت و امور اداری | اداری</t>
+          <t>خدمات مشتری و شخصی | ریاضیات | زبان انگلیسی | مدیریت و اداره | اداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | وضوح گفتار | حساسیت به مسئله | استدلال ریاضی | توانایی کار با اعداد | استدلال قیاسی | ترتیب‌دهی به اطلاعات | تشخیص گفتار | درک کتبی | توجه انتخابی | استدلال استقرایی | بیان کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | حساسیت به مسئله | استدلال ریاضی | توانایی عددی | استدلال قیاسی | ترتیب‌دهی اطلاعات | تشخیص گفتار | درک کتبی | توجه انتخابی | استدلال استقرایی | بیان کتبی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>اهمیت دقیق یا منظم بودن | ارتباط با دیگران | داخل ساختمان، محیط کنترل‌شده | اهمیت تکرار وظایف مشابه | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | نزدیکی فیزیکی | صرف زمان به صورت ایستاده | فراوانی تصمیم‌گیری | پیامد خطا | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض صداها و سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>اهمیت دقیق یا درست بودن | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت تکرار وظایف یکسان | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | نزدیکی فیزیکی | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | پیامد خطا | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | صندوقداران | تعمیرکاران و سرویس‌کاران ماشین‌های سکه‌ای، فروش خودکار و تفریحی | کارمندان باجه و اجاره | تاییدکنندگان، بررسی‌کنندگان و کارمندان اعتبار | سرپرستان خط اول کارکنان خدمات قمار | کارکنان پول خرد و صندوقداران باجه قمار | دیلرهای قمار | مدیران قمار | ماموران نظارت بر قمار و بازرسان قمار | نویسندگان و دوندگان دفاتر شرط‌بندی قمار و ورزشی | کارمندان پذیرش هتل، متل و اقامتگاه | کارمندان حساب‌های جدید | کارمندان حقوق و دستمزد و ثبت زمان | دستیاران داروخانه | فروشندگان خرده‌فروشی | انبارداران و پرکنندگان سفارش | تحویل‌داران بانک</t>
+          <t>کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | صندوق‌داران | سرویس‌کاران و تعمیرکاران ماشین‌های سکه‌ای، فروش خودکار و تفریحی | کارمندان باجه و اجاره | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | سرپرستان خط اول کارگران خدمات قمار | صندوق‌داران غرفه و مسئولان پول خرد قماربازی | دیلرهای قمار | مدیران قماربازی | ماموران نظارت بر قمار و بازرسان قمار | نویسندگان و دوندگان دفاتر شرط‌بندی ورزشی و قمار | کارمندان پذیرش هتل، متل و اقامتگاه | کارمندان حساب‌های جدید | کارمندان حقوق و دستمزد و ثبت زمان | دستیاران داروخانه | فروشندگان خرده‌فروشی | قفسه‌چین‌ها و پرکننده‌های سفارش | تحویل‌داران</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ADP Enterprise HR | ADP PC/Payroll | ADP Workforce Now | ADP eTIME | API Navigator | Asure Software HCM | نرم‌افزار حقوق و دستمزد خودکار | نرم‌افزار ثبت زمان خودکار | BMH Open4 Payroll | BSI ComplianceFactory | CyberShift Workforce Management 3G Time and Attendance | نرم‌افزار ورود داده | EBS On Line InstaPay | نرم‌افزار ایمیل | نرم‌افزار حسابداری وجوه امانی | Galaxy Technologies TimeStar Enterprise | Human Resource MicroSystems HR Entre | نرم‌افزار مدیریت منابع انسانی HRMS | IBM Cognos Impromptu | IBM Notes | Intuit QuickBooks | Jantek Jupiter Time Attendance | Kronos Workforce Payroll | Kronos Workforce Timekeeper | MicroFocus GroupWise | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Great Plains Personal Data Keeper | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | NetSuite ERP | Netscape Navigator | NuView EBS | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle HRIS | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Payroll for North America | PDS Vista | PayData Advanced HR | نرم‌افزار حقوق و دستمزد Paychex | نرم‌افزار حقوق و دستمزد | نرم‌افزار Penta | Quicken | RSM McGladrey Clear Pay | SAP Americas mySAP ERP Human Capital Management HCM | SAP Crystal Reports | نرم‌افزار SAP | Sage 50 Accounting | Sage HRMS | نرم‌افزار مالیات | TimePlus Payroll | UNITIME | Ultimate Software UltiPro Workplace | Virtual Software Virtual Timecard | نرم‌افزار مرورگر وب | WorkForce Software EmpCenter Time and Attendance | نرم‌افزار Workday | isolved Time</t>
+          <t>ADP Enterprise HR | ADP PC/Payroll | ADP Workforce Now | ADP eTIME | API Navigator | Asure Software HCM | نرم‌افزار حقوق و دستمزد خودکار | نرم‌افزار ثبت زمان خودکار | BMH Open4 Payroll | BSI ComplianceFactory | CyberShift Workforce Management 3G Time and Attendance | نرم‌افزار ورود داده | EBS On Line InstaPay | نرم‌افزار ایمیل | نرم‌افزار حسابداری صندوق | Galaxy Technologies TimeStar Enterprise | Human Resource MicroSystems HR Entre | نرم‌افزار مدیریت منابع انسانی HRMS | IBM Cognos Impromptu | IBM Notes | Intuit QuickBooks | Jantek Jupiter Time Attendance | Kronos Workforce Payroll | Kronos Workforce Timekeeper | MicroFocus GroupWise | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Great Plains Personal Data Keeper | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | NetSuite ERP | Netscape Navigator | NuView EBS | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle HRIS | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Payroll for North America | PDS Vista | PayData Advanced HR | نرم‌افزار حقوق و دستمزد Paychex | نرم‌افزار حقوق و دستمزد | نرم‌افزار Penta | Quicken | RSM McGladrey Clear Pay | SAP Americas mySAP ERP Human Capital Management HCM | SAP Crystal Reports | نرم‌افزار SAP | Sage 50 Accounting | Sage HRMS | نرم‌افزار مالیاتی | TimePlus Payroll | UNITIME | Ultimate Software UltiPro Workplace | Virtual Software Virtual Timecard | نرم‌افزار مرورگر وب | WorkForce Software EmpCenter Time and Attendance | نرم‌افزار Workday | isolved Time</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش‌دادن فعالانه | ریاضیات | نگارش | سخن‌گفتن | تفکر انتقادی | مانیتورینگ</t>
+          <t>درک مطلب | گوش دادن فعال | ریاضیات | نگارش | سخن گفتن | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>اداری | ریاضیات | زبان انگلیسی | اقتصاد و حسابداری | پرسنل و منابع انسانی | مدیریت و امور اداری | خدمات مشتریان و شخصی | کامپیوتر و الکترونیک</t>
+          <t>اداری | ریاضیات | زبان انگلیسی | اقتصاد و حسابداری | پرسنل و منابع انسانی | مدیریت و اداره | خدمات مشتری و شخصی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان کتبی | دید نزدیک | بیان شفاهی | استدلال ریاضی | توانایی کار با اعداد | ترتیب‌دهی به اطلاعات | حساسیت به مسئله | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | توجه انتخابی</t>
+          <t>درک شفاهی | درک کتبی | بیان کتبی | بینایی نزدیک | بیان شفاهی | استدلال ریاضی | توانایی عددی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>اهمیت دقیق یا منظم بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان به صورت نشسته | مکالمات تلفنی | ایمیل | اهمیت تکرار وظایف مشابه | کار با یا مشارکت در یک گروه کاری یا تیم | داخل ساختمان، محیط کنترل‌شده | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | مکالمات تلفنی | ایمیل | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | مدیران خدمات اداری | کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | تحلیلگران بودجه | مدیران جبران خدمات و مزایا | متخصصان جبران خدمات، مزایا و تجزیه و تحلیل شغل | تاییدکنندگان، بررسی‌کنندگان و کارمندان اعتبار | مصاحبه‌کنندگان واجد شرایط، برنامه‌های دولتی | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | مدیران مالی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | متخصصان منابع انسانی | کارمندان دفتری، عمومی | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | ممیزان و وصول‌کنندگان مالیات، و ماموران دارایی | تهیه‌کنندگان اظهارنامه مالیاتی | خزانه‌داران و کنترلرها</t>
+          <t>حسابداران و حسابرسان | مدیران خدمات اداری | کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | تحلیلگران بودجه | مدیران جبران خدمات و مزایا | متخصصان جبران خدمات، مزایا و تحلیل شغل | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | مدیران مالی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | متخصصان منابع انسانی | کارمندان دفتری عمومی | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد | تهیه‌کنندگان اظهارنامه مالیاتی | خزانه‌داران و کنترل‌کنندگان</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Autotask | نرم‌افزار تبادل الکترونیکی داده EDI | IBM Maximo Asset Management | Intuit QuickBooks | نرم‌افزار ردیابی موجودی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Oracle Database | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Radiant Systems CounterPoint | SAP Business Objects | نرم‌افزار SAP | نرم‌افزار مرورگر وب | نرم‌افزار برنامه‌ریزی کاری</t>
+          <t>Autotask | نرم‌افزار تبادل الکترونیکی داده EDI | IBM Maximo Asset Management | Intuit QuickBooks | نرم‌افزار ردیابی موجودی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Oracle Database | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Radiant Systems CounterPoint | SAP Business Objects | نرم‌افزار SAP | نرم‌افزار مرورگر وب | نرم‌افزار زمان‌بندی کار</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن‌گفتن | درک مطلب | گوش‌دادن فعالانه | تفکر انتقادی | نگارش | مانیتورینگ | یادگیری فعالانه | ریاضیات</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | تفکر انتقادی | نگارش | نظارت | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | اداری | خدمات مشتریان و شخصی | اقتصاد و حسابداری | مدیریت و امور اداری | ریاضیات | کامپیوتر و الکترونیک | حمل‌ونقل</t>
+          <t>زبان انگلیسی | اداری | خدمات مشتری و شخصی | اقتصاد و حسابداری | مدیریت و اداره | ریاضیات | رایانه و الکترونیک | حمل و نقل</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | دید نزدیک | بیان کتبی | ترتیب‌دهی به اطلاعات | وضوح گفتار | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | تشخیص گفتار | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بینایی نزدیک | بیان کتبی | ترتیب‌دهی اطلاعات | وضوح گفتار | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | تشخیص گفتار | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | اهمیت دقیق یا منظم بودن | ارتباط با دیگران | اهمیت تکرار وظایف مشابه | فراوانی تصمیم‌گیری | تعیین وظایف, اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان به صورت نشسته | تاثیر تصمیمات بر همکاران یا نتایج شرکت | داخل ساختمان، محیط کنترل‌شده</t>
+          <t>ایمیل | مکالمات تلفنی | اهمیت دقیق یا درست بودن | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | خریداران و ماموران خرید، محصولات کشاورزی | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | متخصصان لجستیک | تحلیلگران لجستیک | کارمندان دفتری، عمومی | کارمندان ثبت سفارش | کارمندان خدمات پستی | کارمندان تولید، برنامه‌ریزی و تسریع | ماموران خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | کارمندان ارسال، دریافت و موجودی | انبارداران و پرکنندگان سفارش | مدیران زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
+          <t>کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | خریداران و نمایندگان خرید، محصولات کشاورزی | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | لجستیسین‌ها | تحلیلگران لجستیک | کارمندان دفتری عمومی | کارمندان ثبت سفارش | کارمندان خدمات پستی | کارمندان تولید، برنامه‌ریزی و هماهنگی | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | کارمندان ارسال، دریافت و موجودی کالا | قفسه‌چین‌ها و پرکننده‌های سفارش | مدیران زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0065_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0065_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | زبان انگلیسی | اداری | رایانه و الکترونیک | پرسنلی و منابع انسانی | اقتصاد و حسابداری</t>
+          <t>مدیریت و اداره | خدمات مشتری و شخصی | زبان انگلیسی | اداری | رایانه و الکترونیک | پرسنل و منابع انسانی | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | دید نزدیک | استدلال استقرایی | ابتکار | روانی ایده‌ها | انعطاف‌پذیری طبقه‌بندی | توجه انتخابی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | بینایی نزدیک | استدلال استقرایی | اصالت | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | سرپرستان رده‌اول کارگران ساختمانی و استخراج | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی، به‌جز خدمات قمار | سرپرستان رده‌اول کارکنان تهیه و سرو غذا | سرپرستان رده‌اول کارگران کمکی، باربران و جابه‌جا‌کنندگان دستی کالا | سرپرستان رده‌اول کارکنان خدمات و نظافت | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی مواد | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول کارشناسان فروش غیرخرده‌فروشی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول ارائه‌دهندگان خدمات فردی | سرپرستان رده‌اول کارکنان تولید و عملیات | سرپرستان رده‌اول کارکنان فروش خرده‌فروشی | سرپرستان رده‌اول کارکنان حراست و نگهبانی | مدیران کل و مدیران ارشد عملیاتی | دستیاران منابع انسانی، به‌جز امور حقوق و دستمزد و ثبت زمان | کارشناسان منابع انسانی | تحلیل‌گران مدیریت و فرآیندها | کارمندان امور اداری و دفتری عمومی | کارشناسان مدیریت پروژه</t>
+          <t>مدیران خدمات اداری و پشتیبانی | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سرپرستان رده اول کارگران تولید و عملیات | سرپرستان رده‌اول فروشندگان خرده‌فروشی | سرپرستان رده‌اول کارکنان حراست و انتظامات | مدیران کل و مدیران عملیات | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | کارشناسان منابع انسانی | کارشناسان تحلیل مدیریت و روش‌ها | متصدیان امور دفتری و امور عمومی اداری | کارشناسان مدیریت پروژه</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | اداری | رایانه و الکترونیک | مخابرات</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | رایانه و الکترونیک | مخابرات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | دید نزدیک | توجه انتخابی | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان کتبی | درک کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان کتبی | درک کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان کارگزاری | کارشناسان خدمات مشتریان | کاربران ورود اطلاعات | متصدیان اعزام و دیسپچ، به‌جز پلیس، آتش‌نشانی و اورژانس | مسئولان دفاتر و دستیاران اجرایی مدیریت | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارمندان امور مراسلات و اپراتورهای ماشین‌های پستی، به‌جز پست دولتی | منشی‌ها و مسئولان دفاتر پزشکی | کارمندان امور اداری و دفتری عمومی | باجه‌داران و متصدیان خدمات پستی | اپراتورهای مخابراتی فوریت‌های عمومی و ایمنی | متصدیان پذیرش و کارمندان پذیرش و اطلاعات | منشی‌ها و مسئولان دفاتر اداری، به‌جز حقوقی، پزشکی و اجرایی | کارشناسان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به‌جز خطوط ارتباطی | بازاریابان تلفنی | اپراتورهای تلفن | تایپیست‌ها و کاربران پردازش متن</t>
+          <t>مدیران خدمات اداری و پشتیبانی | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارشناسان امور اداری و معاملات کارگزاری | کارشناسان خدمات و پشتیبانی مشتریان | متصدیان ورود اطلاعات و داده‌آمایی | متصدیان دیسپاچ و اعزام | مسئولان دفاتر و دستیاران اجرایی مدیریت | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارمندان امور مراسلات و متصدیان ماشین‌های پستی، به جز پست دولتی | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | متصدیان امور دفتری و امور عمومی اداری | متصدیان باجه و امور پستی | اپراتورهای فوریت‌های پلیسی و امدادی | متصدیان پذیرش و اطلاعات | منشی‌ها و دستیاران اداری عمومی | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان | کارشناسان بازاریابی تلفنی | اپراتورهای تلفن | تایپیست‌ها و متصدیان حروف‌چینی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مخابرات | اداری | زبان انگلیسی | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | مخابرات | اداری | زبان انگلیسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | دید نزدیک | توجه انتخابی | حساسیت به مسئله | درک کتبی</t>
+          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | توجه انتخابی | حساسیت به مسئله | درک کتبی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | صندوق‌داران | کارشناسان پشتیبانی شبکه‌های رایانه‌ای | کارشناسان خدمات مشتریان | کاربران ورود اطلاعات | متصدیان اعزام و دیسپچ، به‌جز پلیس، آتش‌نشانی و اورژانس | کارمندان بایگانی | کارمندان پردازش خسارت و صدور بیمه‌نامه | پرسشگران، به‌جز حوزه تسهیلات و اعتبارسنجی | منشی‌ها و مسئولان دفاتر پزشکی | کارمندان امور اداری و دفتری عمومی | اپراتورهای مخابراتی فوریت‌های عمومی و ایمنی | متصدیان پذیرش و کارمندان پذیرش و اطلاعات | متصدیان صدور بلیت و کارمندان آژانس‌های مسافرتی | کارشناسان فروش خدمات، به‌جز تبلیغات، بیمه، خدمات مالی و مسافرتی | منشی‌ها و مسئولان دفاتر اداری، به‌جز حقوقی، پزشکی و اجرایی | اپراتورهای مراکز تلفن و پاسخگویی | نصابان و تعمیرکاران تجهیزات مخابراتی، به‌جز خطوط ارتباطی | بازاریابان تلفنی | تایپیست‌ها و کاربران پردازش متن</t>
+          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | صندوق‌داران | متخصصان پشتیبانی شبکه رایانه‌ای | کارشناسان خدمات و پشتیبانی مشتریان | متصدیان ورود اطلاعات و داده‌آمایی | متصدیان دیسپاچ و اعزام | متصدیان بایگانی و اسناد | کارمندان پردازش خسارت و بیمه‌نامه‌ها | پرسشگران و مصاحبه‌گران، به جز امور وام و تعیین صلاحیت | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | متصدیان امور دفتری و امور عمومی اداری | اپراتورهای فوریت‌های پلیسی و امدادی | متصدیان پذیرش و اطلاعات | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | منشی‌ها و دستیاران اداری عمومی | اپراتورهای مراکز تلفن و پاسخگویی | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان | کارشناسان بازاریابی تلفنی | تایپیست‌ها و متصدیان حروف‌چینی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مخابرات | خدمات مشتریان و خدمات فردی | زبان انگلیسی | رایانه و الکترونیک | ارتباطات و رسانه | ایمنی و امنیت عمومی</t>
+          <t>مخابرات | خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | ارتباطات و رسانه | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | تسهیم زمان و چندوظیفگی | چابکی انگشتان | چابکی دستی | دید دور | حفظ کردن و به‌خاطرسپاری | روانی ایده‌ها | توجه شنیداری | سرعت درک و تشخیص</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | توجه شنیداری | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورهای مراکز تلفن و پاسخگویی | اپراتورهای تلفن | اپراتورهای مخابراتی فوریت‌های عمومی و ایمنی | متصدیان اعزام و دیسپچ، به‌جز پلیس، آتش‌نشانی و اورژانس | کارشناسان خدمات مشتریان | متصدیان پذیرش و کارمندان پذیرش و اطلاعات | متصدیان صدور بلیت و کارمندان آژانس‌های مسافرتی | کارمندان ثبت و پیگیری سفارش‌ها | کارمندان امور مکاتبات و دبیرخانه | کاربران ورود اطلاعات | کارمندان امور اداری و دفتری عمومی | سایر کارمندان ثبت اسناد و اطلاعات | متصدیان حمل‌ونقل و باربری کالا | نامه‌رسان‌ها و پیک‌ها | بازاریابان تلفنی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارشناسان پشتیبانی کاربران رایانه | نصابان و تعمیرکاران تجهیزات مخابراتی، به‌جز خطوط ارتباطی | تایپیست‌ها و کاربران پردازش متن | سایر کارکنان امور اداری و پشتیبانی</t>
+          <t>اپراتورهای مراکز تلفن و پاسخگویی | اپراتورهای تلفن | اپراتورهای فوریت‌های پلیسی و امدادی | متصدیان دیسپاچ و اعزام | کارشناسان خدمات و پشتیبانی مشتریان | متصدیان پذیرش و اطلاعات | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | متصدیان ثبت و پیگیری سفارش‌ها | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | متصدیان ورود اطلاعات و داده‌آمایی | متصدیان امور دفتری و امور عمومی اداری | سایر متصدیان ثبت اسناد و اطلاعات | کارگزاران حمل‌ونقل و بار | پیک‌ها و نامه‌رسان‌ها | کارشناسان بازاریابی تلفنی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | متخصصان پشتیبانی کاربران رایانه | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان | تایپیست‌ها و متصدیان حروف‌چینی | کارکنان امور دفتری و پشتیبانی اداری، سایر مشاغل</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نگارش | درک مطلب | تفکر انتقادی | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | نگارش | درک مطلب | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | ریاضیات | اقتصاد و حسابداری | حقوق و امور دولتی | رایانه و الکترونیک | اداری | مدیریت و امور اداری</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | اقتصاد و حسابداری | قانون و دولت | رایانه و الکترونیک | اداری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان کتبی | دید نزدیک | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | حساسیت به مسئله</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان کتبی | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | کارمندان کارگزاری | کارمندان امور مکاتبات و دبیرخانه | تحلیل‌گران اعتباری | کارشناسان تأیید، اعتبارسنجی و امور اعتبار | مشاوران اعتباری | کارشناسان خدمات مشتریان | مدیران مالی | کارمندان پردازش خسارت و صدور بیمه‌نامه | مصاحبه‌گران و کارمندان بررسی درخواست تسهیلات | کارشناسان تسهیلات و اعتبارات | کارمندان افتتاح حساب | کارمندان ثبت و پیگیری سفارش‌ها | کارمندان امور حقوق، دستمزد و ثبت زمان | مشاوران مالی شخصی | کارشناسان فروش خدمات، به‌جز تبلیغات، بیمه، خدمات مالی و مسافرتی | ممیزان و مأموران وصول مالیات و کارشناسان امور مالیاتی | تحویل‌داران و متصدیان باجه بانک</t>
+          <t>حسابداران و حسابرسان | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان امور اداری و معاملات کارگزاری | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | مشاوران اعتباری و مدیریت بدهی | کارشناسان خدمات و پشتیبانی مشتریان | مدیران امور مالی | کارمندان پردازش خسارت و بیمه‌نامه‌ها | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و مسئولان تسهیلات و اعتبارات | متصدیان افتتاح حساب | متصدیان ثبت و پیگیری سفارش‌ها | کارمندان امور حقوق، دستمزد و ثبت زمان | مشاوران مالی فردی | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | ممیزان، ماموران وصول و کارشناسان مالیاتی | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | ریاضیات | شنیدن فعال | سخن گفتن | تفکر انتقادی | نظارت | نگارش</t>
+          <t>درک مطلب | ریاضیات | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>اداری | خدمات مشتریان و خدمات فردی | زبان انگلیسی | اقتصاد و حسابداری | ریاضیات | رایانه و الکترونیک | مدیریت و امور اداری</t>
+          <t>اداری | خدمات مشتری و شخصی | زبان انگلیسی | اقتصاد و حسابداری | ریاضیات | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک کتبی | مرتب‌سازی اطلاعات | بیان شفاهی | تشخیص گفتار | بیان کتبی | درک شفاهی | حساسیت به مسئله | وضوح گفتار | توانایی محاسبات عددی | انعطاف‌پذیری طبقه‌بندی | استدلال قیاسی | استدلال استقرایی</t>
+          <t>بینایی نزدیک | درک کتبی | ترتیب‌دهی اطلاعات | بیان شفاهی | تشخیص گفتار | بیان کتبی | درک شفاهی | حساسیت به مسئله | وضوح گفتار | توانایی عددی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان دفترداری، حسابداری و امور حسابرسی | کارمندان کارگزاری | کارمندان امور مکاتبات و دبیرخانه | کارشناسان تأیید، اعتبارسنجی و امور اعتبار | کارشناسان خدمات مشتریان | کارمندان بایگانی | مدیران مالی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارمندان پردازش خسارت و صدور بیمه‌نامه | کارمندان امور اداری و دفتری عمومی | کارمندان ثبت و پیگیری سفارش‌ها | کارمندان امور حقوق، دستمزد و ثبت زمان | باجه‌داران و متصدیان خدمات پستی | کارمندان تدارکات و کارپردازی | کارشناسان فروش خدمات، به‌جز تبلیغات، بیمه، خدمات مالی و مسافرتی | کارمندان انبار، بارگیری، تحویل و موجودی کالا | ممیزان و مأموران وصول مالیات و کارشناسان امور مالیاتی | تحویل‌داران و متصدیان باجه بانک</t>
+          <t>حسابداران و حسابرسان | کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان امور اداری و معاملات کارگزاری | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان خدمات و پشتیبانی مشتریان | متصدیان بایگانی و اسناد | مدیران امور مالی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارمندان پردازش خسارت و بیمه‌نامه‌ها | متصدیان امور دفتری و امور عمومی اداری | متصدیان ثبت و پیگیری سفارش‌ها | کارمندان امور حقوق، دستمزد و ثبت زمان | متصدیان باجه و امور پستی | کارمندان تدارکات و کارپردازی | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارمندان انبار، ارسال و دریافت کالا | ممیزان، ماموران وصول و کارشناسان مالیاتی | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ریاضیات | تفکر انتقادی | شنیدن فعال | درک مطلب | نگارش | سخن گفتن | نظارت</t>
+          <t>ریاضیات | تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | اداری | ریاضیات | زبان انگلیسی | اقتصاد و حسابداری | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | اداری | ریاضیات | زبان انگلیسی | اقتصاد و حسابداری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | استدلال ریاضی | دید نزدیک | درک کتبی | بیان کتبی | توانایی محاسبات عددی | حساسیت به مسئله | بیان شفاهی | تشخیص گفتار | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال استقرایی | وضوح گفتار | توجه انتخابی | استدلال قیاسی</t>
+          <t>درک شفاهی | استدلال ریاضی | بینایی نزدیک | درک کتبی | بیان کتبی | توانایی عددی | حساسیت به مسئله | بیان شفاهی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | وضوح گفتار | توجه انتخابی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان کارگزاری | کارمندان امور مکاتبات و دبیرخانه | تحلیل‌گران اعتباری | کارشناسان تأیید، اعتبارسنجی و امور اعتبار | کارمندان بایگانی | مدیران مالی | کارمندان پردازش خسارت و صدور بیمه‌نامه | مصاحبه‌گران و کارمندان بررسی درخواست تسهیلات | کارشناسان تسهیلات و اعتبارات | کارمندان افتتاح حساب | کارمندان امور اداری و دفتری عمومی | کارمندان امور حقوق، دستمزد و ثبت زمان | کارگزاران و کارشناسان فروش اوراق بهادار، کالا و خدمات مالی | دستیاران آماری | ممیزان و مأموران وصول مالیات و کارشناسان امور مالیاتی | کارشناسان تنظیم اظهارنامه مالیاتی | تحویل‌داران و متصدیان باجه بانک</t>
+          <t>حسابداران و حسابرسان | کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارشناسان امور اداری و معاملات کارگزاری | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | متصدیان بایگانی و اسناد | مدیران امور مالی | کارمندان پردازش خسارت و بیمه‌نامه‌ها | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و مسئولان تسهیلات و اعتبارات | متصدیان افتتاح حساب | متصدیان امور دفتری و امور عمومی اداری | کارمندان امور حقوق، دستمزد و ثبت زمان | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | دستیاران و تکنسین‌های آمار | ممیزان، ماموران وصول و کارشناسان مالیاتی | کارشناسان تنظیم و تسلیم اظهارنامه مالیاتی | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,22 +902,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Office software | Microsoft Word | Microsoft Outlook | سامانه‌های ثبت تراکنش‌های صندوق | نرم‌افزارهای مدیریت اسناد مالی</t>
+          <t>Corel WordPerfect Office Suite | Microsoft Office software | نرم‌افزار Microsoft Office | Microsoft Outlook | سامانه‌های ثبت تراکنش‌های صندوق | نرم‌افزارهای مدیریت اسناد مالی</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | ریاضیات | نظارت | تفکر انتقادی | نگارش | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | ریاضیات | نظارت | تفکر انتقادی | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ریاضیات | زبان انگلیسی | مدیریت و امور اداری | اداری</t>
+          <t>خدمات مشتری و شخصی | ریاضیات | زبان انگلیسی | مدیریت و اداره | اداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | وضوح گفتار | حساسیت به مسئله | استدلال ریاضی | توانایی محاسبات عددی | استدلال قیاسی | مرتب‌سازی اطلاعات | تشخیص گفتار | درک کتبی | توجه انتخابی | استدلال استقرایی | بیان کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | حساسیت به مسئله | استدلال ریاضی | توانایی عددی | استدلال قیاسی | ترتیب‌دهی اطلاعات | تشخیص گفتار | درک کتبی | توجه انتخابی | استدلال استقرایی | بیان کتبی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | کارمندان کارگزاری | صندوق‌داران | سرویس‌کاران و تعمیرکاران ماشین‌های سکه‌ای، فروش خودکار و تفریحی | کارمندان پیشخوان و کرایه کالا | کارشناسان تأیید، اعتبارسنجی و امور اعتبار | سرپرستان رده‌اول کارکنان خدمات مراکز تفریحی و بازی | مسئولان خرد کردن پول و صندوق‌داران باجه‌های بازی | متصدیان و دیلرهای بازی | مدیران سالن‌های بازی و مراکز سرگرمی | مأموران حراست، پایش و بازرسان سالن‌های بازی | نویسندگان و متصدیان ثبت پیش‌بینی و رویدادهای ورزشی | کارمندان پذیرش هتل، متل و اقامتگاه | کارمندان افتتاح حساب | کارمندان امور حقوق، دستمزد و ثبت زمان | کمک‌داروسازان و پرسنل کمکی داروخانه | فروشندگان خرده‌فروشی | انبارداران و متصدیان جمع‌آوری سفارش‌ها | تحویل‌داران و متصدیان باجه بانک</t>
+          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان امور اداری و معاملات کارگزاری | صندوق‌داران | سرویس‌کاران و تعمیرکاران دستگاه‌های سکه‌ای، فروش خودکار و بازی | متصدیان باجه و کرایه کالا و خدمات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | سرپرستان رده‌اول کارکنان خدمات مراکز بازی و سرگرمی | صندوق‌داران و متصدیان تبدیل ژتون و وجه در مراکز تفریحی | گردانندگان بازی‌های میزی و کازینویی | مدیران سالن‌ها و بازی‌های تفریحی دارای مجوز | ماموران و بازرسان نظارت تصویری و پایش اماکن سرگرمی و بازی | متصدیان ثبت و پرداخت شرط‌بندی‌های ورزشی و سرگرمی | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | متصدیان افتتاح حساب | کارمندان امور حقوق، دستمزد و ثبت زمان | کمک‌متصدیان داروخانه | فروشندگان خرده‌فروشی | متصدیان چیدمان و آماده‌سازی سفارش | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | ریاضیات | نگارش | سخن گفتن | تفکر انتقادی | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | ریاضیات | نگارش | سخن گفتن | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>اداری | ریاضیات | زبان انگلیسی | اقتصاد و حسابداری | پرسنلی و منابع انسانی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک</t>
+          <t>اداری | ریاضیات | زبان انگلیسی | اقتصاد و حسابداری | پرسنل و منابع انسانی | مدیریت و اداره | خدمات مشتری و شخصی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان کتبی | دید نزدیک | بیان شفاهی | استدلال ریاضی | توانایی محاسبات عددی | مرتب‌سازی اطلاعات | حساسیت به مسئله | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | توجه انتخابی</t>
+          <t>درک شفاهی | درک کتبی | بیان کتبی | بینایی نزدیک | بیان شفاهی | استدلال ریاضی | توانایی عددی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | مدیران خدمات اداری | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | تحلیل‌گران بودجه | مدیران حقوق و مزایا | کارشناسان جبران خدمت، مزایا و تجزیه‌وتحلیل شغل | کارشناسان تأیید، اعتبارسنجی و امور اعتبار | مصاحبه‌گران تعیین واجدین شرایط در برنامه‌های دولتی | مسئولان دفاتر و دستیاران اجرایی مدیریت | کارمندان بایگانی | مدیران مالی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | دستیاران منابع انسانی، به‌جز امور حقوق و دستمزد و ثبت زمان | کارشناسان منابع انسانی | کارمندان امور اداری و دفتری عمومی | منشی‌ها و مسئولان دفاتر اداری، به‌جز حقوقی، پزشکی و اجرایی | ممیزان و مأموران وصول مالیات و کارشناسان امور مالیاتی | کارشناسان تنظیم اظهارنامه مالیاتی | خزانه‌داران و مدیران کنترل مالی</t>
+          <t>حسابداران و حسابرسان | مدیران خدمات اداری و پشتیبانی | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | تحلیل‌گران بودجه | مدیران جبران خدمت و مزایا | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | مسئولان دفاتر و دستیاران اجرایی مدیریت | متصدیان بایگانی و اسناد | مدیران امور مالی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | کارشناسان منابع انسانی | متصدیان امور دفتری و امور عمومی اداری | منشی‌ها و دستیاران اداری عمومی | ممیزان، ماموران وصول و کارشناسان مالیاتی | کارشناسان تنظیم و تسلیم اظهارنامه مالیاتی | خزانه‌داران و مدیران مالی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | شنیدن فعال | تفکر انتقادی | نگارش | نظارت | یادگیری فعال | ریاضیات</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | تفکر انتقادی | نگارش | نظارت | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | اداری | خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری | مدیریت و امور اداری | ریاضیات | رایانه و الکترونیک | ترابری و حمل‌ونقل</t>
+          <t>زبان انگلیسی | اداری | خدمات مشتری و شخصی | اقتصاد و حسابداری | مدیریت و اداره | ریاضیات | رایانه و الکترونیک | حمل و نقل</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | دید نزدیک | بیان کتبی | مرتب‌سازی اطلاعات | وضوح گفتار | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | تشخیص گفتار | استدلال ریاضی | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بینایی نزدیک | بیان کتبی | ترتیب‌دهی اطلاعات | وضوح گفتار | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | تشخیص گفتار | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | کارمندان کارگزاری | خریداران و مأموران خرید محصولات کشاورزی | کارمندان پیشخوان و کرایه کالا | کارشناسان خدمات مشتریان | متخصصان لجستیک و زنجیره تأمین | تحلیل‌گران لجستیک | کارمندان امور اداری و دفتری عمومی | کارمندان ثبت و پیگیری سفارش‌ها | باجه‌داران و متصدیان خدمات پستی | کارمندان برنامه‌ریزی تولید و تسریع در سفارش‌ها | مأموران خرید، به‌جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید و تدارکات | کارشناسان فروش خدمات، به‌جز تبلیغات، بیمه، خدمات مالی و مسافرتی | کارمندان انبار، بارگیری، تحویل و موجودی کالا | انبارداران و متصدیان جمع‌آوری سفارش‌ها | مدیران زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع | خریداران عمده‌فروشی و خرده‌فروشی، به‌جز محصولات کشاورزی</t>
+          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان امور اداری و معاملات کارگزاری | خریداران و کارشناسان خرید محصولات کشاورزی | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | متصدیان امور دفتری و امور عمومی اداری | متصدیان ثبت و پیگیری سفارش‌ها | متصدیان باجه و امور پستی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارشناسان خرید و امور قراردادها | مدیران خرید و تدارکات | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارمندان انبار، ارسال و دریافت کالا | متصدیان چیدمان و آماده‌سازی سفارش | مدیران زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
